--- a/artfynd/A 25672-2024 artfynd.xlsx
+++ b/artfynd/A 25672-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6333224</v>
+        <v>2680981</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224913</v>
+        <v>220164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Irsta, 375 m NO kyrkan, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596620.8098013519</v>
+        <v>596621</v>
       </c>
       <c r="R2" t="n">
-        <v>6608153.167366388</v>
+        <v>6608153</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,24 +750,14 @@
           <t>2011-06-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-06-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Öppen glänta i blandskog gränsande mot åker. Med stenblock och berghäll. Inom ca 17 m + 7 stjälkar 4-5 meter bort bakom en i skogskant. Rester av stengärdesgård i utkanten, men inget bete nu. Tips från Marie Flennersjö.</t>
+          <t>En stor och glädjande överraskning att finna solvända här!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2680981</v>
+        <v>15944477</v>
       </c>
       <c r="B3" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,24 +817,31 @@
           <t>(L.) Mill.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Irsta, 375 m NO kyrkan, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596620.8098013519</v>
+        <v>596613</v>
       </c>
       <c r="R3" t="n">
-        <v>6608153.167366388</v>
+        <v>6608151</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,27 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-06-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-06-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En stor och glädjande överraskning att finna solvända här!</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15944477</v>
+        <v>4430192</v>
       </c>
       <c r="B4" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,36 +916,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220164</v>
+        <v>222133</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -990,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596612.7372623937</v>
+        <v>596621</v>
       </c>
       <c r="R4" t="n">
-        <v>6608151.439967649</v>
+        <v>6608153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,22 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,61 +1012,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15944526</v>
+        <v>15944467</v>
       </c>
       <c r="B5" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224913</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Irsta, 375 m NO kyrkan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596612.7372623937</v>
+        <v>596613</v>
       </c>
       <c r="R5" t="n">
-        <v>6608151.439967649</v>
+        <v>6608151</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,24 +1085,9 @@
           <t>2014-06-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>8 plantor med 2+7x1 stjälkar i frukt, varav en i östra skogskanten bakom enar. Minst 45 vegetativa plantor (svårt att avgränsa plantorna), varav ca 20 i den östra skogskanten bakom enar. Använde tidigare koordinater. Dagens koordinater: 1551201, 6609269 och 1551191, 6609270 (skogskant bakom enar). Tog bort små skott av asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15944479</v>
+        <v>5145590</v>
       </c>
       <c r="B6" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,21 +1148,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Irsta, 375 m NO kyrkan, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596612.7372623937</v>
+        <v>596621</v>
       </c>
       <c r="R6" t="n">
-        <v>6608151.439967649</v>
+        <v>6608153</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,22 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1322,15 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5145590</v>
+        <v>15944479</v>
       </c>
       <c r="B7" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,16 +1250,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Irsta, 375 m NO kyrkan, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596620.8098013519</v>
+        <v>596613</v>
       </c>
       <c r="R7" t="n">
-        <v>6608153.167366388</v>
+        <v>6608151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,22 +1291,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-06-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-06-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,15 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>93789238</v>
+        <v>6333224</v>
       </c>
       <c r="B8" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,24 +1352,34 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östergården, Vstm</t>
+          <t>Irsta, 375 m NO kyrkan, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596626.2057523755</v>
+        <v>596621</v>
       </c>
       <c r="R8" t="n">
-        <v>6608140.645376882</v>
+        <v>6608153</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,22 +1403,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2011-06-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2011-06-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Öppen glänta i blandskog gränsande mot åker. Med stenblock och berghäll. Inom ca 17 m + 7 stjälkar 4-5 meter bort bakom en i skogskant. Rester av stengärdesgård i utkanten, men inget bete nu. Tips från Marie Flennersjö.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,27 +1422,257 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Gräs- och rismark i låglandet</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Öppen glänta i blandskog med block och berghäll, gränsande mot åker</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15944526</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Irsta, 375 m NO kyrkan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596613</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6608151</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Irsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-06-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-06-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>8 plantor med 2+7x1 stjälkar i frukt, varav en i östra skogskanten bakom enar. Minst 45 vegetativa plantor (svårt att avgränsa plantorna), varav ca 20 i den östra skogskanten bakom enar. Använde tidigare koordinater. Dagens koordinater: 1551201, 6609269 och 1551191, 6609270 (skogskant bakom enar). Tog bort små skott av asp.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Öppen glänta i blandskog med block och berghäll, gränsande mot åker</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>93789238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Östergården, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596626</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6608140</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Irsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Gräs- och rismark i låglandet</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Sara Hagström Yamamoto</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Sara Hagström Yamamoto</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25672-2024 artfynd.xlsx
+++ b/artfynd/A 25672-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2680981</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15944477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4430192</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15944467</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5145590</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15944479</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6333224</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15944526</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,8 +1718,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93789238</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>